--- a/resources/templates/standard/J4200-01.xlsx
+++ b/resources/templates/standard/J4200-01.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="34">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>2025년 도면 일치성 점검 체크시트</t>
   </si>
@@ -741,12 +744,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -780,15 +785,15 @@
       <c r="AI1" s="2"/>
       <c r="AJ1" s="2"/>
       <c r="AK1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM1" s="4"/>
       <c r="AN1" s="4"/>
       <c r="AO1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP1" s="4"/>
       <c r="AQ1" s="4"/>
@@ -885,27 +890,27 @@
     </row>
     <row r="4" ht="21" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
       <c r="J4" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
       <c r="M4" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N4" s="9"/>
       <c r="O4" s="9"/>
@@ -919,7 +924,7 @@
       <c r="W4" s="9"/>
       <c r="X4" s="9"/>
       <c r="Y4" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z4" s="8"/>
       <c r="AA4" s="8"/>
@@ -937,7 +942,7 @@
       <c r="AM4" s="8"/>
       <c r="AN4" s="8"/>
       <c r="AO4" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP4" s="8"/>
       <c r="AQ4" s="8"/>
@@ -1003,35 +1008,35 @@
         <v>12</v>
       </c>
       <c r="Y5" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z5" s="11"/>
       <c r="AA5" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB5" s="11"/>
       <c r="AC5" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD5" s="11"/>
       <c r="AE5" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF5" s="11"/>
       <c r="AG5" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH5" s="12"/>
       <c r="AI5" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ5" s="12"/>
       <c r="AK5" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL5" s="12"/>
       <c r="AM5" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN5" s="11"/>
       <c r="AO5" s="8"/>
@@ -1055,71 +1060,71 @@
       <c r="L6" s="16"/>
       <c r="M6" s="17"/>
       <c r="N6" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
       <c r="Q6" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R6" s="17"/>
       <c r="S6" s="17"/>
       <c r="T6" s="18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U6" s="17"/>
       <c r="V6" s="17"/>
       <c r="W6" s="18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X6" s="17"/>
       <c r="Y6" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z6" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA6" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB6" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC6" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AD6" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE6" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF6" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG6" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH6" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI6" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ6" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK6" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL6" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM6" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN6" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO6" s="16"/>
       <c r="AP6" s="16"/>
@@ -1151,52 +1156,52 @@
       <c r="W7" s="18"/>
       <c r="X7" s="17"/>
       <c r="Y7" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z7" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA7" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB7" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC7" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AD7" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE7" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF7" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG7" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH7" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI7" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ7" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK7" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL7" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM7" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN7" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO7" s="16"/>
       <c r="AP7" s="16"/>
@@ -1230,52 +1235,52 @@
       <c r="W8" s="18"/>
       <c r="X8" s="17"/>
       <c r="Y8" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z8" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA8" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB8" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC8" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AD8" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE8" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF8" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG8" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH8" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI8" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ8" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK8" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL8" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM8" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN8" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO8" s="16"/>
       <c r="AP8" s="16"/>
@@ -1307,52 +1312,52 @@
       <c r="W9" s="18"/>
       <c r="X9" s="17"/>
       <c r="Y9" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z9" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA9" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB9" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC9" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AD9" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE9" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF9" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG9" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH9" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI9" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ9" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK9" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL9" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM9" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN9" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO9" s="16"/>
       <c r="AP9" s="16"/>
@@ -1386,52 +1391,52 @@
       <c r="W10" s="18"/>
       <c r="X10" s="17"/>
       <c r="Y10" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z10" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA10" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB10" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC10" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AD10" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE10" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF10" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG10" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH10" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI10" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ10" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK10" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL10" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM10" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN10" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO10" s="16"/>
       <c r="AP10" s="16"/>
@@ -1463,52 +1468,52 @@
       <c r="W11" s="18"/>
       <c r="X11" s="17"/>
       <c r="Y11" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z11" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA11" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB11" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC11" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AD11" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE11" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF11" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG11" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH11" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI11" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ11" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK11" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL11" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM11" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN11" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO11" s="16"/>
       <c r="AP11" s="16"/>
@@ -1542,52 +1547,52 @@
       <c r="W12" s="18"/>
       <c r="X12" s="17"/>
       <c r="Y12" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z12" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA12" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB12" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC12" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AD12" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE12" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF12" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG12" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH12" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI12" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ12" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK12" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL12" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM12" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN12" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO12" s="16"/>
       <c r="AP12" s="16"/>
@@ -1619,52 +1624,52 @@
       <c r="W13" s="18"/>
       <c r="X13" s="17"/>
       <c r="Y13" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z13" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA13" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB13" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC13" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AD13" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE13" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF13" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG13" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH13" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI13" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ13" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK13" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL13" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM13" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN13" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO13" s="16"/>
       <c r="AP13" s="16"/>
@@ -1698,52 +1703,52 @@
       <c r="W14" s="18"/>
       <c r="X14" s="18"/>
       <c r="Y14" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z14" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA14" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB14" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC14" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AD14" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE14" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF14" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG14" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH14" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI14" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ14" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK14" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL14" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM14" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN14" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO14" s="19"/>
       <c r="AP14" s="19"/>
@@ -1775,52 +1780,52 @@
       <c r="W15" s="18"/>
       <c r="X15" s="18"/>
       <c r="Y15" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z15" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA15" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB15" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC15" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AD15" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE15" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF15" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG15" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH15" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI15" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ15" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK15" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL15" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM15" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN15" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO15" s="19"/>
       <c r="AP15" s="19"/>
@@ -1854,52 +1859,52 @@
       <c r="W16" s="18"/>
       <c r="X16" s="18"/>
       <c r="Y16" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z16" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA16" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB16" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC16" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AD16" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE16" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF16" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG16" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH16" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI16" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ16" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK16" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL16" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM16" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN16" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO16" s="19"/>
       <c r="AP16" s="19"/>
@@ -1931,52 +1936,52 @@
       <c r="W17" s="18"/>
       <c r="X17" s="18"/>
       <c r="Y17" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z17" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA17" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB17" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC17" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AD17" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE17" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF17" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG17" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH17" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI17" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ17" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK17" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL17" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM17" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN17" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO17" s="19"/>
       <c r="AP17" s="19"/>
@@ -2010,52 +2015,52 @@
       <c r="W18" s="18"/>
       <c r="X18" s="18"/>
       <c r="Y18" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z18" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA18" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB18" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC18" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AD18" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE18" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF18" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG18" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH18" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI18" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ18" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK18" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL18" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM18" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN18" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO18" s="19"/>
       <c r="AP18" s="19"/>
@@ -2087,52 +2092,52 @@
       <c r="W19" s="18"/>
       <c r="X19" s="18"/>
       <c r="Y19" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z19" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA19" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB19" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC19" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AD19" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE19" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF19" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG19" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH19" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI19" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ19" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK19" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL19" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM19" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN19" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO19" s="19"/>
       <c r="AP19" s="19"/>
@@ -2140,7 +2145,7 @@
     </row>
     <row r="20" ht="21" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" s="20"/>
       <c r="C20" s="20"/>
@@ -2187,7 +2192,7 @@
     </row>
     <row r="21" ht="21" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A21" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
@@ -2234,7 +2239,7 @@
     </row>
     <row r="22" ht="21" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B22" s="22"/>
       <c r="C22" s="22"/>
@@ -2258,7 +2263,7 @@
       <c r="U22" s="22"/>
       <c r="V22" s="23"/>
       <c r="W22" s="23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X22" s="23"/>
       <c r="Y22" s="23"/>
@@ -2283,7 +2288,7 @@
     </row>
     <row r="23" ht="21" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
@@ -2307,7 +2312,7 @@
       <c r="U23" s="22"/>
       <c r="V23" s="23"/>
       <c r="W23" s="23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="X23" s="23"/>
       <c r="Y23" s="23"/>
@@ -2332,7 +2337,7 @@
     </row>
     <row r="24" ht="21" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A24" s="22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B24" s="22"/>
       <c r="C24" s="22"/>
@@ -2356,7 +2361,7 @@
       <c r="U24" s="22"/>
       <c r="V24" s="23"/>
       <c r="W24" s="23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X24" s="23"/>
       <c r="Y24" s="23"/>
@@ -2381,7 +2386,7 @@
     </row>
     <row r="25" ht="21" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A25" s="24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="24"/>
       <c r="C25" s="24"/>
@@ -2405,7 +2410,7 @@
       <c r="U25" s="24"/>
       <c r="V25" s="25"/>
       <c r="W25" s="25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X25" s="25"/>
       <c r="Y25" s="25"/>
